--- a/adminfiles/smthg_NYC_scouting_base_v1.xlsx
+++ b/adminfiles/smthg_NYC_scouting_base_v1.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@vaquera.nyc</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@zoegustaviaannawhalen</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@gabe.gordon</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@janewade_</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@mel___usine</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@colleenallen</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@meruert__tolegen</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@wiederhoeft_</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@greedyunit</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>@tanner.fletcher</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
